--- a/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_405_R46.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_405_R46.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7724</v>
+        <v>3.5105</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4106</v>
+        <v>4.7608</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.6382</v>
+        <v>-1.2503</v>
       </c>
       <c r="G2" t="n">
         <v>3.1807</v>
@@ -610,13 +610,13 @@
         <v>0.9099</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.7049</v>
+        <v>-0.9668</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7183</v>
+        <v>-0.3681</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9866</v>
+        <v>-0.5987</v>
       </c>
       <c r="V2" t="n">
         <v>0.3867</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3646</v>
+        <v>1.9516</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6601</v>
+        <v>1.8935</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7045</v>
+        <v>0.0581</v>
       </c>
       <c r="G3" t="n">
         <v>1.4401</v>
@@ -688,13 +688,13 @@
         <v>1.3648</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5987</v>
+        <v>-1.0117</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6583</v>
+        <v>-0.4248</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0595</v>
+        <v>-0.5869</v>
       </c>
       <c r="V3" t="n">
         <v>0.1583</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4516</v>
+        <v>0.9919</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0971</v>
+        <v>2.8636</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.6455</v>
+        <v>-1.8718</v>
       </c>
       <c r="G4" t="n">
         <v>2.9743</v>
@@ -766,13 +766,13 @@
         <v>1.3648</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.2524</v>
+        <v>-1.7121</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-0.7481</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7377</v>
+        <v>-0.964</v>
       </c>
       <c r="V4" t="n">
         <v>-1.6352</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0615</v>
+        <v>-0.5868</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6636</v>
+        <v>0.0799</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.602</v>
+        <v>-0.6667</v>
       </c>
       <c r="G5" t="n">
         <v>1.2492</v>
@@ -844,13 +844,13 @@
         <v>0.9099</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1867</v>
+        <v>-0.8351</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6946</v>
+        <v>0.1109</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8813</v>
+        <v>-0.9459</v>
       </c>
       <c r="V5" t="n">
         <v>-0.7734</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.2662</v>
+        <v>-1.1297</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0199</v>
+        <v>0.2135</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2463</v>
+        <v>-1.3432</v>
       </c>
       <c r="G6" t="n">
         <v>-0.9022</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3639</v>
+        <v>-0.2274</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5028</v>
+        <v>-0.2693</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1388</v>
+        <v>0.0419</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>J. MONTERO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5327</v>
+        <v>-1.7161</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4656</v>
+        <v>-0.6933</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.9983</v>
+        <v>-1.0228</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7372</v>
+        <v>-1.8517</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2595</v>
+        <v>-0.7463</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4776</v>
+        <v>-1.1054</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.09710000000000001</v>
+        <v>0.4759</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2089</v>
+        <v>-0.1819</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1118</v>
+        <v>0.6577</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.64</v>
+        <v>-2.3276</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0506</v>
+        <v>-0.5645</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5894</v>
+        <v>-1.7631</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.4549</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.2747</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.8198</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2946</v>
+        <v>-1.0445</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5628</v>
+        <v>-0.5296</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2682</v>
+        <v>-0.515</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0901</v>
+        <v>1.6352</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.6352</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0901</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. THOMPSON</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.7302</v>
+        <v>-1.8183</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0159</v>
+        <v>0.1154</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.7143</v>
+        <v>-1.9337</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2416</v>
+        <v>-0.7372</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1748</v>
+        <v>-0.2595</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4164</v>
+        <v>-0.4776</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6568000000000001</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3297</v>
+        <v>-0.2089</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.3271</v>
+        <v>0.1118</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4152</v>
+        <v>-0.64</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5044</v>
+        <v>-0.0506</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0893</v>
+        <v>-0.5894</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2275</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2275</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.6259</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3591</v>
+        <v>0.2126</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.2668</v>
+        <v>-0.2036</v>
       </c>
       <c r="V8" t="n">
         <v>-1.0901</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. MONTERO</t>
+          <t>D. THOMPSON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.9606</v>
+        <v>-2.3675</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7439</v>
+        <v>-0.7825</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2167</v>
+        <v>-1.585</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.8517</v>
+        <v>-0.2416</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7463</v>
+        <v>0.1748</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1054</v>
+        <v>-0.4164</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4759</v>
+        <v>-0.6568000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1819</v>
+        <v>-0.3297</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6577</v>
+        <v>-0.3271</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.3276</v>
+        <v>0.4152</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5645</v>
+        <v>0.5044</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.7631</v>
+        <v>-0.0893</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4549</v>
+        <v>0.2275</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2747</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8198</v>
+        <v>0.2275</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.2891</v>
+        <v>-1.2632</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.5802</v>
+        <v>-0.1257</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7089</v>
+        <v>-1.1375</v>
       </c>
       <c r="V9" t="n">
-        <v>1.6352</v>
+        <v>-1.0901</v>
       </c>
       <c r="W9" t="n">
-        <v>1.6352</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.0901</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6533</v>
+        <v>-3.991</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.101</v>
+        <v>-0.5679</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.5523</v>
+        <v>-3.4231</v>
       </c>
       <c r="G10" t="n">
         <v>0.3921</v>
@@ -1234,13 +1234,13 @@
         <v>0.2275</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9554</v>
+        <v>-1.293</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2036</v>
+        <v>-0.2633</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.159</v>
+        <v>-1.0297</v>
       </c>
       <c r="V10" t="n">
         <v>-2.1802</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K. TAYLOR</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.5878</v>
+        <v>-5.0461</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6485</v>
+        <v>-2.9366</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.9392</v>
+        <v>-2.1095</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4675</v>
+        <v>-3.5764</v>
       </c>
       <c r="H11" t="n">
-        <v>2.5909</v>
+        <v>-0.1226</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.1234</v>
+        <v>-3.4538</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1401</v>
+        <v>-1.967</v>
       </c>
       <c r="K11" t="n">
-        <v>3.5004</v>
+        <v>0.2187</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.3603</v>
+        <v>-2.1857</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.6726</v>
+        <v>-1.6094</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9095</v>
+        <v>-0.3413</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.7631</v>
+        <v>-1.2681</v>
       </c>
       <c r="P11" t="n">
-        <v>-4.0945</v>
+        <v>1.8198</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.6868</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5923</v>
+        <v>1.8198</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1294</v>
+        <v>-1.1792</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8982</v>
+        <v>-0.9696</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7688</v>
+        <v>-0.2097</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0901</v>
+        <v>-2.1102</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0901</v>
+        <v>-2.1102</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>K. TAYLOR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.61</v>
+        <v>-5.4893</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.4035</v>
+        <v>-2.5824</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.2065</v>
+        <v>-2.9069</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.5764</v>
+        <v>0.4675</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1226</v>
+        <v>2.5909</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.4538</v>
+        <v>-2.1234</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.967</v>
+        <v>3.1401</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2187</v>
+        <v>3.5004</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.1857</v>
+        <v>-0.3603</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.6094</v>
+        <v>-2.6726</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3413</v>
+        <v>-0.9095</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.2681</v>
+        <v>-1.7631</v>
       </c>
       <c r="P12" t="n">
-        <v>1.8198</v>
+        <v>-4.0945</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-5.6868</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8198</v>
+        <v>1.5923</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.7431</v>
+        <v>-0.7722</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.4365</v>
+        <v>-0.0357</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3066</v>
+        <v>-0.7365</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.1102</v>
+        <v>-1.0901</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.1102</v>
+        <v>-1.0901</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-15.6907</v>
+        <v>-15.6908</v>
       </c>
       <c r="E13" t="n">
-        <v>2.364299999999998</v>
+        <v>2.363999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-18.0548</v>
+        <v>-18.0549</v>
       </c>
       <c r="G13" t="n">
         <v>2.394800000000001</v>
@@ -1447,7 +1447,7 @@
         <v>10.0611</v>
       </c>
       <c r="L13" t="n">
-        <v>3.8399</v>
+        <v>3.839899999999999</v>
       </c>
       <c r="M13" t="n">
         <v>-11.5062</v>
@@ -1459,7 +1459,7 @@
         <v>-10.5122</v>
       </c>
       <c r="P13" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>-10.2363</v>
@@ -1468,16 +1468,16 @@
         <v>10.2363</v>
       </c>
       <c r="S13" t="n">
-        <v>-10.2961</v>
+        <v>-10.2962</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.4106</v>
+        <v>-3.4107</v>
       </c>
       <c r="U13" t="n">
-        <v>-6.885599999999998</v>
+        <v>-6.8856</v>
       </c>
       <c r="V13" t="n">
-        <v>-7.7891</v>
+        <v>-7.789099999999999</v>
       </c>
       <c r="W13" t="n">
         <v>2.1102</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.9707</v>
+        <v>7.3083</v>
       </c>
       <c r="E14" t="n">
-        <v>6.4732</v>
+        <v>6.9402</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4975</v>
+        <v>0.3682</v>
       </c>
       <c r="G14" t="n">
         <v>1.6773</v>
@@ -1546,13 +1546,13 @@
         <v>1.8198</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3625</v>
+        <v>1.7001</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4312</v>
+        <v>0.8982</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9312</v>
+        <v>0.8018999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>2.3386</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.4583</v>
+        <v>5.4472</v>
       </c>
       <c r="E15" t="n">
-        <v>3.8231</v>
+        <v>3.0059</v>
       </c>
       <c r="F15" t="n">
-        <v>2.6352</v>
+        <v>2.4413</v>
       </c>
       <c r="G15" t="n">
         <v>1.5515</v>
@@ -1624,13 +1624,13 @@
         <v>1.3648</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8159</v>
+        <v>1.8048</v>
       </c>
       <c r="T15" t="n">
-        <v>2.0834</v>
+        <v>1.2662</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7325</v>
+        <v>0.5386</v>
       </c>
       <c r="V15" t="n">
         <v>1.8635</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.0726</v>
+        <v>4.5353</v>
       </c>
       <c r="E16" t="n">
-        <v>6.1534</v>
+        <v>4.5191</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0808</v>
+        <v>0.0162</v>
       </c>
       <c r="G16" t="n">
         <v>-0.4069</v>
@@ -1702,13 +1702,13 @@
         <v>1.1374</v>
       </c>
       <c r="S16" t="n">
-        <v>3.7762</v>
+        <v>2.2389</v>
       </c>
       <c r="T16" t="n">
-        <v>3.568</v>
+        <v>1.9337</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2082</v>
+        <v>0.3051</v>
       </c>
       <c r="V16" t="n">
         <v>1.7935</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.8132</v>
+        <v>3.1239</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3808</v>
+        <v>2.4975</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4324</v>
+        <v>0.6264</v>
       </c>
       <c r="G17" t="n">
         <v>0.4172</v>
@@ -1780,13 +1780,13 @@
         <v>0.6824</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7399</v>
+        <v>1.0505</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6706</v>
+        <v>0.7873</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0693</v>
+        <v>0.2632</v>
       </c>
       <c r="V17" t="n">
         <v>2.3386</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.0431</v>
+        <v>2.291</v>
       </c>
       <c r="E18" t="n">
-        <v>3.0585</v>
+        <v>3.759</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0154</v>
+        <v>-1.468</v>
       </c>
       <c r="G18" t="n">
         <v>-0.8045</v>
@@ -1858,13 +1858,13 @@
         <v>0.6824</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3025</v>
+        <v>1.5504</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3833</v>
+        <v>1.0837</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9192</v>
+        <v>0.4667</v>
       </c>
       <c r="V18" t="n">
         <v>1.0901</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. OKEKE</t>
+          <t>U. GARUBA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5925</v>
+        <v>0.2827</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6872</v>
+        <v>0.1482</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0946</v>
+        <v>0.1345</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.743</v>
+        <v>-0.8603</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2787</v>
+        <v>-1.0517</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0217</v>
+        <v>0.1914</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.07920000000000001</v>
+        <v>0.0822</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9144</v>
+        <v>-0.8491</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.9936</v>
+        <v>0.9313</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6637999999999999</v>
+        <v>-0.9425</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6357</v>
+        <v>-0.2026</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.028</v>
+        <v>-0.7399</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3648</v>
+        <v>1.1374</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3648</v>
+        <v>1.1374</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0608</v>
+        <v>0.5507</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7664</v>
+        <v>0.066</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2944</v>
+        <v>0.4847</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0901</v>
+        <v>-0.5451</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0901</v>
+        <v>-0.5451</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1772</v>
+        <v>0.2095</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1772</v>
+        <v>0.2095</v>
       </c>
       <c r="G20" t="n">
         <v>0.1556</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0215</v>
+        <v>0.0539</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0215</v>
+        <v>0.0539</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1772</v>
+        <v>0.2095</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1772</v>
+        <v>0.2095</v>
       </c>
       <c r="G21" t="n">
         <v>0.1556</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0215</v>
+        <v>0.0539</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0215</v>
+        <v>0.0539</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>U. GARUBA</t>
+          <t>C. OKEKE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1915</v>
+        <v>0.0735</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.5522</v>
+        <v>0.1035</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3608</v>
+        <v>-0.03</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.8603</v>
+        <v>-0.743</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.0517</v>
+        <v>0.2787</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1914</v>
+        <v>-1.0217</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0822</v>
+        <v>-0.07920000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.8491</v>
+        <v>0.9144</v>
       </c>
       <c r="L22" t="n">
-        <v>0.9313</v>
+        <v>-0.9936</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.9425</v>
+        <v>-0.6637999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2026</v>
+        <v>-0.6357</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7399</v>
+        <v>-0.028</v>
       </c>
       <c r="P22" t="n">
-        <v>1.1374</v>
+        <v>1.3648</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1374</v>
+        <v>1.3648</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0765</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6344</v>
+        <v>0.1827</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7109</v>
+        <v>0.3591</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5451</v>
+        <v>-1.0901</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5451</v>
+        <v>-1.0901</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.274</v>
+        <v>-0.4105</v>
       </c>
       <c r="E23" t="n">
-        <v>1.335</v>
+        <v>1.1016</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6091</v>
+        <v>-1.5121</v>
       </c>
       <c r="G23" t="n">
         <v>-1.524</v>
@@ -2248,13 +2248,13 @@
         <v>0.4549</v>
       </c>
       <c r="S23" t="n">
-        <v>0.795</v>
+        <v>0.6585</v>
       </c>
       <c r="T23" t="n">
-        <v>0.8381999999999999</v>
+        <v>0.6047</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0432</v>
+        <v>0.0538</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,10 +2281,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.7386</v>
+        <v>-1.6218</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.7584</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="F24" t="n">
         <v>-0.9802</v>
@@ -2326,10 +2326,10 @@
         <v>0.2275</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2993</v>
+        <v>-0.1826</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1437</v>
+        <v>-0.0269</v>
       </c>
       <c r="U24" t="n">
         <v>-0.1556</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.4101</v>
+        <v>-5.7579</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.5458</v>
+        <v>-3.3784</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.8643</v>
+        <v>-2.3795</v>
       </c>
       <c r="G25" t="n">
         <v>-0.3465</v>
@@ -2404,13 +2404,13 @@
         <v>1.3648</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.3768</v>
+        <v>0.2754</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.0774</v>
+        <v>0.09</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2994</v>
+        <v>0.1855</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>15.6906</v>
+        <v>15.6907</v>
       </c>
       <c r="E26" t="n">
-        <v>18.0548</v>
+        <v>18.055</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.3641</v>
+        <v>-2.3642</v>
       </c>
       <c r="G26" t="n">
         <v>-2.3948</v>
@@ -2473,7 +2473,7 @@
         <v>-3.84</v>
       </c>
       <c r="P26" t="n">
-        <v>8.881784197001252e-16</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>-10.2364</v>
@@ -2482,13 +2482,13 @@
         <v>10.2362</v>
       </c>
       <c r="S26" t="n">
-        <v>10.2962</v>
+        <v>10.2963</v>
       </c>
       <c r="T26" t="n">
         <v>6.8856</v>
       </c>
       <c r="U26" t="n">
-        <v>3.4105</v>
+        <v>3.410799999999999</v>
       </c>
       <c r="V26" t="n">
         <v>7.789099999999999</v>
